--- a/medals.xlsx
+++ b/medals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1a7c66da9d715b7/Documents/Programmation/Projets/JO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{07755FD8-B111-43A7-B476-B20DE7E62687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEB59E79-A340-4F81-98D2-ACC61CE3B793}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{07755FD8-B111-43A7-B476-B20DE7E62687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7AA4BD5-83FE-4196-90ED-563DD5234C04}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2100" windowWidth="38700" windowHeight="15435" xr2:uid="{D2B8125A-29B7-4C06-B61A-A9B6608FEC34}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="111">
   <si>
     <t>year</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>Milan-Cortina</t>
+  </si>
+  <si>
+    <t> Estonia</t>
   </si>
 </sst>
 </file>
@@ -418,6 +421,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -737,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93C4F19-007F-4AB0-A7F1-BC34F3655C22}">
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:K123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -3308,7 +3315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2024</v>
       </c>
@@ -3340,7 +3347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2024</v>
       </c>
@@ -3372,7 +3379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2024</v>
       </c>
@@ -3404,7 +3411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2024</v>
       </c>
@@ -3436,7 +3443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2024</v>
       </c>
@@ -3468,7 +3475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>2024</v>
       </c>
@@ -3500,7 +3507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2024</v>
       </c>
@@ -3532,7 +3539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2024</v>
       </c>
@@ -3564,7 +3571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2024</v>
       </c>
@@ -3596,7 +3603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2024</v>
       </c>
@@ -3628,7 +3635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2024</v>
       </c>
@@ -3660,7 +3667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2024</v>
       </c>
@@ -3692,7 +3699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2024</v>
       </c>
@@ -3724,7 +3731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>2026</v>
       </c>
@@ -3747,16 +3754,19 @@
         <v>42</v>
       </c>
       <c r="H94">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I94">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J94">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="K94">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>2026</v>
       </c>
@@ -3779,16 +3789,19 @@
         <v>102</v>
       </c>
       <c r="H95">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I95">
         <v>12</v>
       </c>
       <c r="J95">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="K95">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2026</v>
       </c>
@@ -3808,19 +3821,22 @@
         <v>116</v>
       </c>
       <c r="G96" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H96">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I96">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J96">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="K96">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2026</v>
       </c>
@@ -3840,19 +3856,22 @@
         <v>116</v>
       </c>
       <c r="G97" t="s">
+        <v>35</v>
+      </c>
+      <c r="H97">
         <v>10</v>
       </c>
-      <c r="H97">
+      <c r="I97">
         <v>6</v>
       </c>
-      <c r="I97">
-        <v>8</v>
-      </c>
       <c r="J97">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="K97">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2026</v>
       </c>
@@ -3872,19 +3891,22 @@
         <v>116</v>
       </c>
       <c r="G98" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H98">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I98">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J98">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="K98">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2026</v>
       </c>
@@ -3904,19 +3926,22 @@
         <v>116</v>
       </c>
       <c r="G99" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="H99">
+        <v>8</v>
+      </c>
+      <c r="I99">
+        <v>9</v>
+      </c>
+      <c r="J99">
         <v>6</v>
       </c>
-      <c r="I99">
-        <v>6</v>
-      </c>
-      <c r="J99">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K99">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2026</v>
       </c>
@@ -3936,19 +3961,22 @@
         <v>116</v>
       </c>
       <c r="G100" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="H100">
+        <v>8</v>
+      </c>
+      <c r="I100">
         <v>6</v>
-      </c>
-      <c r="I100">
-        <v>4</v>
       </c>
       <c r="J100">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K100">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2026</v>
       </c>
@@ -3968,19 +3996,22 @@
         <v>116</v>
       </c>
       <c r="G101" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="H101">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I101">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J101">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K101">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2026</v>
       </c>
@@ -4011,8 +4042,11 @@
       <c r="J102">
         <v>5</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K102">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2026</v>
       </c>
@@ -4043,8 +4077,11 @@
       <c r="J103">
         <v>12</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K103">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2026</v>
       </c>
@@ -4067,16 +4104,19 @@
         <v>11</v>
       </c>
       <c r="H104">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I104">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J104">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="K104">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2026</v>
       </c>
@@ -4099,16 +4139,19 @@
         <v>29</v>
       </c>
       <c r="H105">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I105">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J105">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="K105">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2026</v>
       </c>
@@ -4128,19 +4171,22 @@
         <v>116</v>
       </c>
       <c r="G106" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H106">
         <v>3</v>
       </c>
       <c r="I106">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J106">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="K106">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2026</v>
       </c>
@@ -4160,19 +4206,22 @@
         <v>116</v>
       </c>
       <c r="G107" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H107">
         <v>3</v>
       </c>
       <c r="I107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="K107">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2026</v>
       </c>
@@ -4192,19 +4241,22 @@
         <v>116</v>
       </c>
       <c r="G108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J108">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="K108">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2026</v>
       </c>
@@ -4233,10 +4285,13 @@
         <v>2</v>
       </c>
       <c r="J109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="K109">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2026</v>
       </c>
@@ -4267,8 +4322,11 @@
       <c r="J110">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K110">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2026</v>
       </c>
@@ -4297,10 +4355,13 @@
         <v>0</v>
       </c>
       <c r="J111">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="K111">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2026</v>
       </c>
@@ -4331,8 +4392,11 @@
       <c r="J112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2026</v>
       </c>
@@ -4363,8 +4427,11 @@
       <c r="J113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2026</v>
       </c>
@@ -4395,8 +4462,11 @@
       <c r="J114">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K114">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2026</v>
       </c>
@@ -4427,8 +4497,11 @@
       <c r="J115">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K115">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2026</v>
       </c>
@@ -4457,10 +4530,13 @@
         <v>1</v>
       </c>
       <c r="J116">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="K116">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2026</v>
       </c>
@@ -4491,8 +4567,11 @@
       <c r="J117">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2026</v>
       </c>
@@ -4512,7 +4591,7 @@
         <v>116</v>
       </c>
       <c r="G118" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -4523,8 +4602,11 @@
       <c r="J118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2026</v>
       </c>
@@ -4544,7 +4626,7 @@
         <v>116</v>
       </c>
       <c r="G119" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -4555,8 +4637,11 @@
       <c r="J119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2026</v>
       </c>
@@ -4576,19 +4661,22 @@
         <v>116</v>
       </c>
       <c r="G120" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H120">
         <v>0</v>
       </c>
       <c r="I120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2026</v>
       </c>
@@ -4608,15 +4696,88 @@
         <v>116</v>
       </c>
       <c r="G121" t="s">
+        <v>103</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>2026</v>
+      </c>
+      <c r="B122" t="s">
+        <v>107</v>
+      </c>
+      <c r="C122" t="s">
+        <v>108</v>
+      </c>
+      <c r="D122" t="s">
+        <v>109</v>
+      </c>
+      <c r="E122">
+        <v>92</v>
+      </c>
+      <c r="F122">
+        <v>116</v>
+      </c>
+      <c r="G122" t="s">
+        <v>47</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>2</v>
+      </c>
+      <c r="K122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>2026</v>
+      </c>
+      <c r="B123" t="s">
+        <v>107</v>
+      </c>
+      <c r="C123" t="s">
+        <v>108</v>
+      </c>
+      <c r="D123" t="s">
+        <v>109</v>
+      </c>
+      <c r="E123">
+        <v>92</v>
+      </c>
+      <c r="F123">
+        <v>116</v>
+      </c>
+      <c r="G123" t="s">
         <v>46</v>
       </c>
-      <c r="H121">
-        <v>0</v>
-      </c>
-      <c r="I121">
-        <v>0</v>
-      </c>
-      <c r="J121">
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="K123">
         <v>1</v>
       </c>
     </row>
